--- a/Top Gainers/Gainer_info.xlsx
+++ b/Top Gainers/Gainer_info.xlsx
@@ -458,135 +458,135 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GAP</t>
+          <t>TNXP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Gap, Inc.</t>
+          <t>Tonix Pharmaceuticals Holding Corp.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+3.67</t>
+          <t>+4.54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(+18.84%)</t>
+          <t>(+27.89%)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>JBSAY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LandBridge Company LLC</t>
+          <t>JBS S.A.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>67.72</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+6.21</t>
+          <t>+2.02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(+10.10%)</t>
+          <t>(+17.34%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>FINV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rigetti Computing, Inc.</t>
+          <t>FinVolution Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+0.84</t>
+          <t>+1.57</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(+9.87%)</t>
+          <t>(+17.25%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>TME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>e.l.f. Beauty, Inc.</t>
+          <t>Tencent Music Entertainment Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>70.68</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+6.26</t>
+          <t>+1.86</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(+9.72%)</t>
+          <t>(+14.24%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TGTX</t>
+          <t>TKAMY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TG Therapeutics, Inc.</t>
+          <t>thyssenkrupp AG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.44</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+3.25</t>
+          <t>+1.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(+9.24%)</t>
+          <t>(+13.93%)</t>
         </is>
       </c>
     </row>
